--- a/AAII_Financials/Quarterly/UFGSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UFGSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
   <si>
     <t>UFGSY</t>
   </si>
@@ -656,76 +656,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -765,8 +768,11 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -806,8 +812,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -847,8 +856,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,8 +876,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -905,8 +918,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,8 +962,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,8 +1006,11 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,8 +1050,11 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,8 +1067,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1083,8 +1109,11 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1124,8 +1153,11 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,8 +1173,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1182,8 +1215,11 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1223,8 +1259,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1264,8 +1303,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1305,8 +1347,11 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1346,8 +1391,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,8 +1435,11 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1428,8 +1479,11 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1469,8 +1523,11 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1567,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1611,11 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1655,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,8 +1699,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1674,8 +1743,11 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1715,8 +1787,11 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,8 +1831,11 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1797,54 +1875,60 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1944,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,131 +1962,141 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1447500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1385500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1384500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1357600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1249500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1773500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1910600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2270400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2286100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2009500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1924200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1586200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1578700</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>988200</v>
+      </c>
+      <c r="E42" s="3">
         <v>725600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>725100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>346400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>318800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>191500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>206300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>82500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>83100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>79600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>76200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>74200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>73900</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2265500</v>
+      </c>
+      <c r="E43" s="3">
         <v>4163400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4160500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3109800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2862100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1639900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1766700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3472600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3496600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1753100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1678700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3847200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3828800</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2041,213 +2136,231 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>764300</v>
+      </c>
+      <c r="E45" s="3">
         <v>789000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>788500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1042900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>959800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1131600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1219000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1367200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1376600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1318700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1262700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1911600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1902400</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5465600</v>
+      </c>
+      <c r="E46" s="3">
         <v>7063500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7058500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5856700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5390200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4736500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5102600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7192800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7242400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5160800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4941800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7419200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7383700</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>88438200</v>
+      </c>
+      <c r="E47" s="3">
         <v>86639700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>86578700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>80947700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>74499600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>67414800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>72625500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>66235900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>66693300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>67398000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>64537500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>64295900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>63988500</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4808600</v>
+      </c>
+      <c r="E48" s="3">
         <v>4972400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4968900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5067500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4663900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4624700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4982200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4967300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5001600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4628100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4431600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3647400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3629900</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2981800</v>
+      </c>
+      <c r="E49" s="3">
         <v>3102000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3099800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2984100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2746400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2648300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2853000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2674400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2692800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2746800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2630200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2556800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2544500</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2400,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,49 +2444,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3599900</v>
+      </c>
+      <c r="E52" s="3">
         <v>3048000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3045900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3525500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3244700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5458100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5880000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3488700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3512800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6483900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6208700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3007600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2993300</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2532,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>106457200</v>
+      </c>
+      <c r="E54" s="3">
         <v>106159400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>106084700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>99726400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>91782300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>86370200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>93046000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>85971300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>86564900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>87828000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>84100300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>82398500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>82004600</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2596,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,49 +2614,53 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>545000</v>
+      </c>
+      <c r="E57" s="3">
         <v>568300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>567900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>621300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>571800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>558000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>601200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>734000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>739000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>712900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>682700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>807900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>804000</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2567,172 +2700,187 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>530100</v>
+      </c>
+      <c r="E59" s="3">
         <v>726800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>726300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>460400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>423700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>223600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>240900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>126400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>127300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>123800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>118500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>755500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>751800</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1363000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1763500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1762300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1376400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1266800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1110900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1196700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1127200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>980700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>950600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>910200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1811100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1802500</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5509000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5880000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5875900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5294200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4872500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5745900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6190100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5947700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5988800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5544400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5309100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5083000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5058700</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>85977400</v>
+      </c>
+      <c r="E62" s="3">
         <v>85844800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>85784300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>81596000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>75096200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>69487500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>74858400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>68952100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>69582500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>70358100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>67371900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>65622300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>65308600</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2920,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2964,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3008,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>92961300</v>
+      </c>
+      <c r="E66" s="3">
         <v>93578700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>93512800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>88347600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>81310000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>76402300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>82307600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>76194100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>76720300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>76996800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>73728800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>72657200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>72309900</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3072,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3114,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3158,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3202,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3246,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5197100</v>
+      </c>
+      <c r="E72" s="3">
         <v>5166100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5162500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4050500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3727800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3597700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3875800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3289400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3312100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3412200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3267400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2272900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2262100</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3334,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3378,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3422,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13176100</v>
+      </c>
+      <c r="E76" s="3">
         <v>12256700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12248000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11067500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10185900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9696700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10446100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8761400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8821900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9060500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8675900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7845000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7807500</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,54 +3510,60 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3409,8 +3603,11 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,49 +3623,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E83" s="3">
         <v>14000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>15100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>231600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>221700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3709,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3753,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3797,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3841,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3885,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="3">
         <v>1071400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1070600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1625400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1495900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>446200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>480700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>886600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>892800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-206100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-197400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1042600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1037600</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,49 +3949,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3">
         <v>-194300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-194200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-122100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-112400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-237600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-256000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-249100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-250800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-365300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-349800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-345000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-343300</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4035,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,49 +4079,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3">
         <v>-868900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-868200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-980600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-902500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-640900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-690400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-819700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-825300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>227700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>218000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-994500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-989800</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,49 +4143,53 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3">
         <v>194900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>194800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>364700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>335600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>12900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>13900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>145700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>146700</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3">
         <v>145200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>144500</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4229,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4273,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,49 +4317,55 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3">
         <v>-188400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-188300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-971800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-894400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-15500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-16700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>94300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>94900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>176300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>168800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-234700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-233600</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4157,45 +4405,51 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>14100</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
         <v>14100</v>
       </c>
       <c r="F102" s="3">
+        <v>14100</v>
+      </c>
+      <c r="G102" s="3">
         <v>-327100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-301000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-210200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-226400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>161300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>162400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>197900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>189500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-186700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-185800</v>
       </c>
     </row>
